--- a/data/trans_dic/P8_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P8_1_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a hacer esfuerzos moderados</t>
+          <t>Población con limitación a hacer esfuerzos moderados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,05</t>
+          <t>0,72; 3,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,48</t>
+          <t>0,81; 3,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,15</t>
+          <t>0,43; 5,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,26</t>
+          <t>1,24; 4,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,49</t>
+          <t>1,99; 5,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,04</t>
+          <t>1,65; 5,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,14</t>
+          <t>0,05; 3,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,11</t>
+          <t>1,26; 3,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,74</t>
+          <t>1,64; 3,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,92</t>
+          <t>1,03; 2,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,74</t>
+          <t>0,55; 4,15</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,53</t>
+          <t>1,86; 4,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,22</t>
+          <t>2,3; 5,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,27</t>
+          <t>2,06; 5,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,67</t>
+          <t>3,12; 8,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,99</t>
+          <t>3,34; 6,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,6</t>
+          <t>3,08; 6,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,6</t>
+          <t>3,05; 6,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,32</t>
+          <t>0,37; 2,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,04</t>
+          <t>2,87; 5,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,3</t>
+          <t>3,03; 5,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,36</t>
+          <t>2,87; 5,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,81</t>
+          <t>1,78; 4,75</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,98</t>
+          <t>2,83; 6,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,35</t>
+          <t>4,38; 8,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,15</t>
+          <t>3,71; 7,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,95</t>
+          <t>3,93; 8,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,36</t>
+          <t>5,96; 10,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 14,07</t>
+          <t>9,01; 13,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,73</t>
+          <t>5,54; 9,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 9,12</t>
+          <t>5,01; 9,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 7,83</t>
+          <t>4,94; 7,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,28; 10,62</t>
+          <t>7,27; 10,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,87</t>
+          <t>5,06; 7,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 7,96</t>
+          <t>5,14; 7,96</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,87</t>
+          <t>5,22; 9,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 13,83</t>
+          <t>8,53; 13,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 14,65</t>
+          <t>9,38; 14,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,55; 71,5</t>
+          <t>10,49; 73,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,37; 18,84</t>
+          <t>12,11; 18,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,6; 19,95</t>
+          <t>13,85; 19,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,01; 19,13</t>
+          <t>12,82; 18,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,14; 16,54</t>
+          <t>11,28; 16,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 13,29</t>
+          <t>9,38; 13,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,88; 15,82</t>
+          <t>11,87; 15,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,8; 15,52</t>
+          <t>11,75; 15,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 56,18</t>
+          <t>12,09; 51,1</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,66; 24,62</t>
+          <t>16,33; 24,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,96; 23,98</t>
+          <t>15,9; 23,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,79; 23,53</t>
+          <t>15,55; 23,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,93; 23,87</t>
+          <t>17,06; 23,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,49; 32,13</t>
+          <t>23,68; 32,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,72; 42,33</t>
+          <t>32,89; 42,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,5; 36,24</t>
+          <t>27,56; 36,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,21; 27,84</t>
+          <t>22,05; 27,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,17; 27,44</t>
+          <t>21,42; 27,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,75; 31,89</t>
+          <t>25,21; 31,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,66; 28,87</t>
+          <t>22,45; 28,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,47; 24,86</t>
+          <t>20,52; 24,88</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,76; 32,88</t>
+          <t>22,62; 32,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,58; 40,86</t>
+          <t>29,02; 40,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,41; 36,17</t>
+          <t>25,75; 35,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,65; 26,58</t>
+          <t>19,74; 26,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,91; 57,99</t>
+          <t>47,82; 57,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,84; 60,05</t>
+          <t>49,37; 60,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,13; 51,99</t>
+          <t>41,9; 52,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,95; 39,77</t>
+          <t>11,21; 39,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,41; 44,76</t>
+          <t>37,8; 45,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41,39; 49,16</t>
+          <t>41,16; 49,05</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35,36; 43,06</t>
+          <t>35,48; 43,1</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,22; 31,7</t>
+          <t>13,08; 31,92</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,54; 60,07</t>
+          <t>46,49; 59,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61,26; 73,17</t>
+          <t>60,89; 73,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49,95; 61,16</t>
+          <t>50,59; 60,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45,55; 54,7</t>
+          <t>44,81; 54,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,77; 80,92</t>
+          <t>70,61; 80,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,31; 84,66</t>
+          <t>76,77; 84,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,7; 74,89</t>
+          <t>64,42; 75,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>70,7; 76,63</t>
+          <t>70,88; 76,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>63,0; 71,14</t>
+          <t>62,6; 70,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72,05; 79,41</t>
+          <t>71,8; 79,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60,35; 68,54</t>
+          <t>60,54; 68,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,83; 67,06</t>
+          <t>61,67; 66,88</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,18; 12,22</t>
+          <t>10,08; 12,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,41; 15,9</t>
+          <t>13,41; 15,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,78; 15,1</t>
+          <t>12,74; 15,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,31; 38,23</t>
+          <t>14,23; 37,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,0; 22,96</t>
+          <t>20,06; 22,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,87; 26,84</t>
+          <t>23,76; 26,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,13; 24,12</t>
+          <t>21,2; 24,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,68; 22,2</t>
+          <t>16,52; 22,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,49; 17,36</t>
+          <t>15,49; 17,21</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,16; 21,2</t>
+          <t>19,15; 21,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17,45; 19,36</t>
+          <t>17,37; 19,3</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,13; 30,76</t>
+          <t>17,14; 29,77</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a hacer esfuerzos moderados</t>
+          <t>Población con limitación a hacer esfuerzos moderados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3624; 15083</t>
+          <t>3559; 15413</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3584; 15811</t>
+          <t>3668; 15073</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 8522</t>
+          <t>0; 8013</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1674; 24596</t>
+          <t>1720; 23009</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6160; 19911</t>
+          <t>5810; 19758</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8478; 23617</t>
+          <t>8560; 24633</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6785; 19950</t>
+          <t>6542; 19964</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>166; 9820</t>
+          <t>163; 9482</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12207; 29913</t>
+          <t>12158; 31892</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14308; 33107</t>
+          <t>14547; 34697</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8431; 23804</t>
+          <t>8370; 22792</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3415; 26657</t>
+          <t>3956; 29614</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13630; 33298</t>
+          <t>13702; 34988</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15241; 35838</t>
+          <t>15801; 35641</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12715; 31108</t>
+          <t>12159; 31017</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13339; 36714</t>
+          <t>13236; 37464</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19998; 43693</t>
+          <t>20912; 43445</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18618; 40254</t>
+          <t>18793; 40944</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16878; 37186</t>
+          <t>17204; 38162</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2157; 11861</t>
+          <t>1877; 12559</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40643; 68601</t>
+          <t>39091; 68613</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38980; 68809</t>
+          <t>39362; 68040</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34096; 61839</t>
+          <t>33170; 60831</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16557; 44999</t>
+          <t>16652; 44417</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17797; 38186</t>
+          <t>18089; 38732</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30337; 56936</t>
+          <t>29867; 54800</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24785; 47831</t>
+          <t>24853; 48888</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20622; 42647</t>
+          <t>21097; 43618</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42829; 71449</t>
+          <t>41091; 70743</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64828; 100005</t>
+          <t>64067; 98469</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37778; 64344</t>
+          <t>36671; 64348</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31308; 53936</t>
+          <t>29658; 54340</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>66217; 103950</t>
+          <t>65677; 100222</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>101324; 147876</t>
+          <t>101201; 144738</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66404; 104732</t>
+          <t>67371; 103366</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57584; 89769</t>
+          <t>57956; 89759</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27361; 51251</t>
+          <t>27116; 49317</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53209; 85032</t>
+          <t>52412; 83987</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59714; 94662</t>
+          <t>60618; 93908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93691; 634774</t>
+          <t>93124; 651048</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63792; 97162</t>
+          <t>62432; 95281</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>83830; 122905</t>
+          <t>85353; 122244</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84467; 124147</t>
+          <t>83228; 120093</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>79403; 117945</t>
+          <t>80405; 117342</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>98279; 137479</t>
+          <t>97030; 138076</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>146197; 194673</t>
+          <t>146101; 195130</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>152872; 200963</t>
+          <t>152206; 203012</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>194008; 899329</t>
+          <t>193600; 817938</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>64441; 95203</t>
+          <t>63143; 94706</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>68540; 102992</t>
+          <t>68277; 102090</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75440; 112451</t>
+          <t>74339; 112047</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>95015; 133947</t>
+          <t>95723; 131986</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>94880; 129806</t>
+          <t>95670; 130826</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>146519; 189567</t>
+          <t>147263; 189341</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>136622; 180068</t>
+          <t>136947; 180883</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>121707; 152547</t>
+          <t>120810; 151045</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>167422; 216978</t>
+          <t>169345; 217474</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>225874; 279742</t>
+          <t>221136; 278242</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>220846; 281381</t>
+          <t>218812; 276315</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>227009; 275740</t>
+          <t>227607; 275996</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66605; 96214</t>
+          <t>66181; 96285</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>91645; 126585</t>
+          <t>89904; 126887</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88284; 120931</t>
+          <t>86101; 119316</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72328; 97858</t>
+          <t>72692; 97194</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>164302; 198864</t>
+          <t>163991; 198227</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>176432; 212564</t>
+          <t>174780; 213261</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>155363; 196390</t>
+          <t>158271; 196994</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>66628; 241957</t>
+          <t>68181; 240062</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>237766; 284487</t>
+          <t>240217; 288977</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>274771; 326345</t>
+          <t>273229; 325577</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>251794; 306626</t>
+          <t>252671; 306895</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>129115; 309603</t>
+          <t>127722; 311730</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>97685; 126075</t>
+          <t>97565; 125215</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>153065; 182817</t>
+          <t>152129; 183803</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>128362; 157174</t>
+          <t>130011; 155735</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>128790; 154656</t>
+          <t>126701; 154340</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>236292; 270200</t>
+          <t>235758; 268114</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>296846; 329299</t>
+          <t>298623; 330230</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>258914; 299691</t>
+          <t>257798; 301847</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>301045; 326319</t>
+          <t>301834; 326576</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>342615; 386876</t>
+          <t>340424; 385758</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>460289; 507276</t>
+          <t>458673; 505000</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>396595; 450418</t>
+          <t>397849; 450175</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>438142; 475182</t>
+          <t>437022; 473920</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>333464; 400371</t>
+          <t>330433; 400334</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>459556; 544870</t>
+          <t>459374; 545048</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>433884; 512592</t>
+          <t>432584; 517136</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>494994; 1322586</t>
+          <t>492165; 1307074</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>675730; 775730</t>
+          <t>677917; 773902</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>849247; 954911</t>
+          <t>845311; 949794</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>748953; 855052</t>
+          <t>751578; 854512</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>619280; 823824</t>
+          <t>613111; 827942</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1030860; 1155726</t>
+          <t>1030826; 1145216</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1338548; 1480716</t>
+          <t>1337813; 1471272</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1211092; 1343531</t>
+          <t>1205297; 1339200</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1228718; 2206264</t>
+          <t>1229176; 2134927</t>
         </is>
       </c>
     </row>
